--- a/Business Statistics/T-Test_Example.xlsx
+++ b/Business Statistics/T-Test_Example.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sneha\OneDrive\Documents\AI-ML LEARNING\Business Statistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5E9626E-72F6-4731-A8AE-E55A59300F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D88BE55-0491-4E0A-AE10-E3AE23D4C6B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{DD60C36A-6BC4-4FF4-8263-B659ACCB759E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{DD60C36A-6BC4-4FF4-8263-B659ACCB759E}"/>
   </bookViews>
   <sheets>
     <sheet name="Z-Test" sheetId="1" r:id="rId1"/>
